--- a/output/excel-export-check.xlsx
+++ b/output/excel-export-check.xlsx
@@ -26,20 +26,20 @@
   <fonts count="3">
     <font>
       <sz val="11"/>
-      <color rgb="FF232D46"/>
-      <name val="Century Gothic"/>
+      <color rgb="FF222222"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="20"/>
-      <color rgb="FF232D46"/>
-      <name val="Century Gothic"/>
+      <sz val="16"/>
+      <color rgb="FF222222"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Century Gothic"/>
+      <color rgb="FF222222"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
@@ -51,7 +51,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF232D46"/>
+        <fgColor rgb="FFEEEEEE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -61,7 +61,9 @@
       <left/>
       <right/>
       <top/>
-      <bottom/>
+      <bottom style="hair">
+        <color rgb="FFDDDDDD"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -76,11 +78,21 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -184,8 +196,48 @@
         <v>629.2</v>
       </c>
     </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VAT</t>
+        </is>
+      </c>
+      <c r="B11" s="4">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COGS</t>
+        </is>
+      </c>
+      <c r="B12" s="4">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gross Profit</t>
+        </is>
+      </c>
+      <c r="B13" s="4">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Net Collected</t>
+        </is>
+      </c>
+      <c r="B14" s="4">
+        <v>1008</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A5:B10"/>
+  <autoFilter ref="A5:B14"/>
   <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
